--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487894_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487894_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9452</v>
+        <v>2.208</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1353</v>
+        <v>-0.8139</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0806</v>
+        <v>3.0218</v>
       </c>
       <c r="G2" t="n">
         <v>2.733</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1821</v>
+        <v>-0.9194</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7581</v>
+        <v>-0.4367</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.424</v>
+        <v>-0.4827</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4371</v>
+        <v>0.5982</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.289</v>
+        <v>-1.5096</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7261</v>
+        <v>2.1078</v>
       </c>
       <c r="G3" t="n">
         <v>-3.6801</v>
@@ -688,13 +688,13 @@
         <v>2.9137</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2584</v>
+        <v>-1.0974</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1207</v>
+        <v>-0.0999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3791</v>
+        <v>-0.9974</v>
       </c>
       <c r="V3" t="n">
         <v>3.5026</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4058</v>
+        <v>-0.1212</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.1976</v>
+        <v>-2.5191</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6034</v>
+        <v>2.3979</v>
       </c>
       <c r="G4" t="n">
         <v>1.3405</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3947</v>
+        <v>-0.9217</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1272</v>
+        <v>-0.1943</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5219</v>
+        <v>-0.7274</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1238</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4024</v>
+        <v>-0.7174</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7731</v>
+        <v>0.5169</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1755</v>
+        <v>-1.2342</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2518</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0268</v>
+        <v>-0.3417</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7358</v>
+        <v>0.4796</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.8213</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1238</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3656</v>
+        <v>-1.7227</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.3065</v>
+        <v>-2.6636</v>
       </c>
       <c r="F6" t="n">
         <v>0.9409999999999999</v>
@@ -922,10 +922,10 @@
         <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.3793</v>
+        <v>-1.7364</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6311</v>
+        <v>-0.9881</v>
       </c>
       <c r="U6" t="n">
         <v>-0.7482</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0564</v>
+        <v>-2.6389</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.923</v>
+        <v>-3.8578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8666</v>
+        <v>1.2189</v>
       </c>
       <c r="G7" t="n">
         <v>1.0544</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.654</v>
+        <v>-2.2364</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2925</v>
+        <v>-1.2272</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3615</v>
+        <v>-1.0092</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. PIEKUS</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1244</v>
+        <v>-2.8933</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1669</v>
+        <v>-0.6878</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9575</v>
+        <v>-2.2055</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1149</v>
+        <v>-0.8067</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5222</v>
+        <v>0.111</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5927</v>
+        <v>-0.9177</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5392</v>
+        <v>-1.374</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1176</v>
+        <v>-1.3504</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5757</v>
+        <v>0.5673</v>
       </c>
       <c r="N8" t="n">
         <v>0.1346</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7103</v>
+        <v>0.4327</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9232</v>
+        <v>-0.9815</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6277</v>
+        <v>0.0805</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2955</v>
+        <v>-1.0621</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3351</v>
+        <v>-1.5213</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X8" t="n">
         <v>-2.3351</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>P. PIEKUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2251</v>
+        <v>-3.0695</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9021</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3229</v>
+        <v>-2.075</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8067</v>
+        <v>-1.1149</v>
       </c>
       <c r="H9" t="n">
-        <v>0.111</v>
+        <v>-0.5222</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9177</v>
+        <v>-0.5927</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.374</v>
+        <v>-0.5392</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0236</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3504</v>
+        <v>0.1176</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5673</v>
+        <v>-0.5757</v>
       </c>
       <c r="N9" t="n">
         <v>0.1346</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4327</v>
+        <v>-0.7103</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3133</v>
+        <v>-0.8682</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1338</v>
+        <v>-0.4553</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1795</v>
+        <v>-0.4129</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5213</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-2.3351</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8612</v>
+        <v>-4.8128</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1197</v>
+        <v>-5.0125</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2584</v>
+        <v>0.1997</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2968</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4802</v>
+        <v>-0.4317</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0562</v>
+        <v>0.051</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.424</v>
+        <v>-0.4827</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2112</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3492</v>
+        <v>-5.1005</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9306</v>
+        <v>-6.3295</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5814</v>
+        <v>1.2291</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1415</v>
@@ -1312,13 +1312,13 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8965</v>
+        <v>-1.6478</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6963</v>
+        <v>-1.0953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2002</v>
+        <v>-0.5525</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.5962</v>
+        <v>-18.2701</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.1976</v>
+        <v>-23.8714</v>
       </c>
       <c r="F12" t="n">
-        <v>5.601599999999999</v>
+        <v>5.601500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7963999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>15.6089</v>
       </c>
       <c r="S12" t="n">
-        <v>-11.5085</v>
+        <v>-11.1822</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.212</v>
+        <v>-3.8857</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.2965</v>
+        <v>-7.296400000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2102</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4642</v>
+        <v>5.972</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5716</v>
+        <v>2.5</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8927</v>
+        <v>3.472</v>
       </c>
       <c r="G13" t="n">
         <v>1.1034</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5065</v>
+        <v>2.0143</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0217</v>
+        <v>0.9502</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4848</v>
+        <v>1.0641</v>
       </c>
       <c r="V13" t="n">
         <v>1.3975</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3878</v>
+        <v>5.784</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5312</v>
+        <v>0.3169</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8566</v>
+        <v>5.4671</v>
       </c>
       <c r="G14" t="n">
         <v>1.1736</v>
@@ -1546,13 +1546,13 @@
         <v>2.7055</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8178</v>
+        <v>2.2139</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1892</v>
+        <v>0.9749</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6285</v>
+        <v>1.239</v>
       </c>
       <c r="V14" t="n">
         <v>2.8127</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8872</v>
+        <v>4.5674</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.4711</v>
       </c>
       <c r="F15" t="n">
-        <v>3.054</v>
+        <v>5.0384</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7303</v>
+        <v>4.984</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6478</v>
+        <v>2.5992</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0825</v>
+        <v>2.3847</v>
       </c>
       <c r="J15" t="n">
-        <v>0.967</v>
+        <v>3.2859</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.7993</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0784</v>
+        <v>1.4867</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7633</v>
+        <v>1.698</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7592</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0041</v>
+        <v>0.8981</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>2.9137</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3681</v>
+        <v>0.9559</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1338</v>
+        <v>0.5292</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5019</v>
+        <v>0.4268</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4599</v>
+        <v>-0.1238</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2646</v>
+        <v>3.7492</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7802</v>
+        <v>1.0475</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4844</v>
+        <v>2.7017</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6254</v>
+        <v>1.7303</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1045</v>
+        <v>1.6478</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5209</v>
+        <v>0.0825</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.6048</v>
+        <v>0.967</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3328</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.272</v>
+        <v>0.0784</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0206</v>
+        <v>0.7633</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7717000000000001</v>
+        <v>0.7592</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7511</v>
+        <v>0.0041</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8712</v>
+        <v>1.2301</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2175</v>
+        <v>0.0805</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6538</v>
+        <v>1.1496</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3538</v>
+        <v>-0.4599</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8137</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2544</v>
+        <v>3.1672</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2927</v>
+        <v>-1.0064</v>
       </c>
       <c r="F17" t="n">
-        <v>4.5472</v>
+        <v>4.1736</v>
       </c>
       <c r="G17" t="n">
-        <v>4.984</v>
+        <v>1.1889</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5992</v>
+        <v>0.3153</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3847</v>
+        <v>0.8736</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2859</v>
+        <v>-0.2276</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7993</v>
+        <v>-0.6317</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4867</v>
+        <v>0.4041</v>
       </c>
       <c r="M17" t="n">
-        <v>1.698</v>
+        <v>1.4164</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8981</v>
+        <v>0.4695</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1624</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9137</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.357</v>
+        <v>1.0189</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2925</v>
+        <v>0.1348</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0645</v>
+        <v>0.8841</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1238</v>
+        <v>1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1238</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7615</v>
+        <v>1.1343</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1851</v>
+        <v>-0.2914</v>
       </c>
       <c r="F18" t="n">
-        <v>3.9465</v>
+        <v>1.4257</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1889</v>
+        <v>-2.6254</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3153</v>
+        <v>-2.1045</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8736</v>
+        <v>-0.5209</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2276</v>
+        <v>-2.6048</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6317</v>
+        <v>-1.3328</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4041</v>
+        <v>-1.272</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4164</v>
+        <v>-0.0206</v>
       </c>
       <c r="N18" t="n">
-        <v>0.947</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4695</v>
+        <v>0.7511</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3868</v>
+        <v>1.7409</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0439</v>
+        <v>1.1459</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6571</v>
+        <v>0.595</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1675</v>
+        <v>0.3538</v>
       </c>
       <c r="W18" t="n">
         <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4146</v>
+        <v>0.2854</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3891</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9745</v>
+        <v>0.9382</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5906</v>
+        <v>-2.1758</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8698</v>
+        <v>-1.6803</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2792</v>
+        <v>-0.4956</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4355</v>
+        <v>-2.0656</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3963</v>
+        <v>-1.3904</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>-0.6752</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1551</v>
+        <v>-0.1103</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4735</v>
+        <v>-0.2899</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3184</v>
+        <v>0.1796</v>
       </c>
       <c r="P19" t="n">
         <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>2.286</v>
+        <v>0.6694</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3479</v>
+        <v>0.2453</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0619</v>
+        <v>0.4241</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.0863</v>
+        <v>1.1675</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.7325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0678</v>
+        <v>0.1265</v>
       </c>
       <c r="E20" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.133</v>
+        <v>0.1917</v>
       </c>
       <c r="G20" t="n">
         <v>0.3796</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3118</v>
+        <v>-0.2531</v>
       </c>
       <c r="T20" t="n">
         <v>-0.06519999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2019</v>
+        <v>-0.4005</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0814</v>
+        <v>-0.4286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8794</v>
+        <v>0.0281</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1758</v>
+        <v>-0.6879</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6803</v>
+        <v>-0.1278</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4956</v>
+        <v>-0.5601</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0656</v>
+        <v>-0.5776</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3904</v>
+        <v>0.0192</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6752</v>
+        <v>-0.5968</v>
       </c>
       <c r="M21" t="n">
         <v>-0.1103</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2899</v>
+        <v>-0.147</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1796</v>
+        <v>0.0367</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>0.182</v>
+        <v>0.0793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1833</v>
+        <v>0.1491</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3654</v>
+        <v>-0.0698</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4387</v>
+        <v>-0.8713</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6429</v>
+        <v>1.1032</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2042</v>
+        <v>-1.9745</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6879</v>
+        <v>1.5906</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1278</v>
+        <v>1.8698</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5601</v>
+        <v>-0.2792</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5776</v>
+        <v>1.4355</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0192</v>
+        <v>1.3963</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5968</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1103</v>
+        <v>0.1551</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.147</v>
+        <v>0.4735</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0367</v>
+        <v>-0.3184</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2081</v>
+        <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0411</v>
+        <v>1.0001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.0621</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1064</v>
+        <v>-0.0619</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-4.0863</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.7325</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3529</v>
+        <v>-1.0593</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7192</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3663</v>
+        <v>1.6599</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1103</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8168</v>
+        <v>1.1104</v>
       </c>
       <c r="T23" t="n">
         <v>0.8663</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0496</v>
+        <v>0.244</v>
       </c>
       <c r="V23" t="n">
         <v>2.565</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9125</v>
+        <v>-2.43</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7202</v>
+        <v>-4.9345</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8077</v>
+        <v>2.5045</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7546</v>
@@ -2326,13 +2326,13 @@
         <v>1.8731</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6746</v>
+        <v>1.157</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4378</v>
+        <v>1.2235</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7633</v>
+        <v>-0.0665</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5838</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.5961</v>
+        <v>20.0249</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6014</v>
+        <v>-5.6015</v>
       </c>
       <c r="F25" t="n">
-        <v>24.1975</v>
+        <v>25.6264</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7964000000000002</v>
+        <v>0.7963999999999993</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9801000000000014</v>
+        <v>0.9801000000000005</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1837999999999997</v>
+        <v>-0.1838000000000002</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.611799999999999</v>
+        <v>-6.611800000000001</v>
       </c>
       <c r="K25" t="n">
         <v>-2.2845</v>
@@ -2404,16 +2404,16 @@
         <v>17.69</v>
       </c>
       <c r="S25" t="n">
-        <v>11.5085</v>
+        <v>12.9371</v>
       </c>
       <c r="T25" t="n">
-        <v>7.2965</v>
+        <v>7.2966</v>
       </c>
       <c r="U25" t="n">
-        <v>4.212000000000001</v>
+        <v>5.640600000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>4.210200000000001</v>
+        <v>4.2102</v>
       </c>
       <c r="W25" t="n">
         <v>9.3225</v>
